--- a/functions.xlsx
+++ b/functions.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dguru\Desktop\forwardDepoloyEngg\pythoncourse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB051527-D9FF-4224-AF72-B01DCE9C33F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F156BD80-4E2A-4671-B2C6-F3BEC991B53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37FE06B5-2CE3-46FE-BDD8-223BA706251D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{37FE06B5-2CE3-46FE-BDD8-223BA706251D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Set" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="122">
   <si>
     <t>LIST</t>
   </si>
@@ -67,12 +68,6 @@
   </si>
   <si>
     <t>remove</t>
-  </si>
-  <si>
-    <t>pop(index)</t>
-  </si>
-  <si>
-    <t>remove the item from the list based on the given index number</t>
   </si>
   <si>
     <t>clear</t>
@@ -173,13 +168,294 @@
   </si>
   <si>
     <t>SET</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>to add a single value into a set</t>
+  </si>
+  <si>
+    <t>update</t>
+  </si>
+  <si>
+    <t>to add a collections of items from one set to another set</t>
+  </si>
+  <si>
+    <t>discard</t>
+  </si>
+  <si>
+    <t>pop</t>
+  </si>
+  <si>
+    <t>(method) def discard(
+ element: object,
+ /
+) -&gt; None
+Remove an element from a set if it is a member.
+Unlike set.remove(), the discard() method does not raise an exception when an element is missing from the set.</t>
+  </si>
+  <si>
+    <t>(method) def remove(
+ element: str,
+ /
+) -&gt; None
+Remove an element from a set; it must be a member.
+If the element is not a member, raise a KeyError.</t>
+  </si>
+  <si>
+    <t>pop(index) 
+pop()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">remove the item from the list based on the given index number
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pop() - removes the last item by default</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For a set, pop() removes and returns an arbitrary item because sets are unordered:
+s = {"apple", "banana", "cherry"}
+item = s.pop()
+print(item)
+print(s)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>possible o/p
+banana
+{'apple', 'cherry'}</t>
+    </r>
+  </si>
+  <si>
+    <t>(function) def sorted(
+ iterable: Iterable[SupportsRichComparisonT@sorted],
+ /,
+ *,
+ key: None = None,
+ reverse: bool = False
+) -&gt; list[SupportsRichComparisonT@sorted]
+Return a new list containing all items from the iterable in ascending order.
+A custom key function can be supplied to customize the sort order, and the reverse flag can be set to request the result in descending order.</t>
+  </si>
+  <si>
+    <t>in / not in</t>
+  </si>
+  <si>
+    <t>union</t>
+  </si>
+  <si>
+    <t>intersection</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>symmetric_difference</t>
+  </si>
+  <si>
+    <t>intersection_update</t>
+  </si>
+  <si>
+    <t>symmetric_difference_update</t>
+  </si>
+  <si>
+    <t>issubset</t>
+  </si>
+  <si>
+    <t>issuperset</t>
+  </si>
+  <si>
+    <t>isdisjoint</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>add()</t>
+  </si>
+  <si>
+    <t>Adds one element</t>
+  </si>
+  <si>
+    <t>s.add(10)</t>
+  </si>
+  <si>
+    <t>update()</t>
+  </si>
+  <si>
+    <t>Adds multiple elements</t>
+  </si>
+  <si>
+    <t>s.update([4, 5])</t>
+  </si>
+  <si>
+    <t>remove()</t>
+  </si>
+  <si>
+    <t>Removes an element; error if missing</t>
+  </si>
+  <si>
+    <t>s.remove(10)</t>
+  </si>
+  <si>
+    <t>discard()</t>
+  </si>
+  <si>
+    <t>Removes an element; no error if missing</t>
+  </si>
+  <si>
+    <t>s.discard(10)</t>
+  </si>
+  <si>
+    <t>pop()</t>
+  </si>
+  <si>
+    <t>Removes and returns an arbitrary element</t>
+  </si>
+  <si>
+    <t>s.pop()</t>
+  </si>
+  <si>
+    <t>clear()</t>
+  </si>
+  <si>
+    <t>Removes all elements</t>
+  </si>
+  <si>
+    <t>s.clear()</t>
+  </si>
+  <si>
+    <t>copy()</t>
+  </si>
+  <si>
+    <t>Creates a shallow copy</t>
+  </si>
+  <si>
+    <t>s.copy()</t>
+  </si>
+  <si>
+    <t>union()</t>
+  </si>
+  <si>
+    <t>Combines sets</t>
+  </si>
+  <si>
+    <t>a.union(b)</t>
+  </si>
+  <si>
+    <t>intersection()</t>
+  </si>
+  <si>
+    <t>Returns common elements</t>
+  </si>
+  <si>
+    <t>a.intersection(b)</t>
+  </si>
+  <si>
+    <t>difference()</t>
+  </si>
+  <si>
+    <t>Returns elements in the first set only</t>
+  </si>
+  <si>
+    <t>a.difference(b)</t>
+  </si>
+  <si>
+    <t>symmetric_difference()</t>
+  </si>
+  <si>
+    <t>Returns elements in either set, but not both</t>
+  </si>
+  <si>
+    <t>a.symmetric_difference(b)</t>
+  </si>
+  <si>
+    <t>issubset()</t>
+  </si>
+  <si>
+    <t>Checks whether a set is a subset</t>
+  </si>
+  <si>
+    <t>a.issubset(b)</t>
+  </si>
+  <si>
+    <t>issuperset()</t>
+  </si>
+  <si>
+    <t>Checks whether a set contains another set</t>
+  </si>
+  <si>
+    <t>a.issuperset(b)</t>
+  </si>
+  <si>
+    <t>isdisjoint()</t>
+  </si>
+  <si>
+    <t>Checks whether sets have no common elements</t>
+  </si>
+  <si>
+    <t>a.isdisjoint(b)</t>
+  </si>
+  <si>
+    <t>intersection_update()</t>
+  </si>
+  <si>
+    <t>Updates a set with common elements</t>
+  </si>
+  <si>
+    <t>a.intersection_update(b)</t>
+  </si>
+  <si>
+    <t>difference_update()</t>
+  </si>
+  <si>
+    <t>Removes elements found in another set</t>
+  </si>
+  <si>
+    <t>a.difference_update(b)</t>
+  </si>
+  <si>
+    <t>symmetric_difference_update()</t>
+  </si>
+  <si>
+    <t>Updates a set with non-common elements</t>
+  </si>
+  <si>
+    <t>a.symmetric_difference_update(b)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,8 +499,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,6 +549,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -334,9 +649,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -352,6 +664,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,55 +1002,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C054CD05-D5B1-4FB2-8D46-D8DA98FB4CAA}">
-  <dimension ref="A5:J30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A5:K48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.7109375" customWidth="1"/>
     <col min="3" max="3" width="103" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="32.140625" customWidth="1"/>
     <col min="9" max="9" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.28515625" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="139.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" ht="46.5" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:11" ht="46.5">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="31.5" x14ac:dyDescent="0.5">
+        <v>45</v>
+      </c>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="31.5">
       <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -727,341 +1064,807 @@
       <c r="I6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="26.25">
       <c r="A7" s="5">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="14"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="26.25">
       <c r="A8" s="5">
         <v>2</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="14"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H8" s="9">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="26.25">
       <c r="A9" s="5">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="14"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+    </row>
+    <row r="10" spans="1:11" ht="26.25">
       <c r="A10" s="5">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="15"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" ht="236.25">
       <c r="A11" s="5">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="14"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="210">
       <c r="A12" s="5">
         <v>6</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>14</v>
+      <c r="B12" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="13"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H12" s="9"/>
+      <c r="I12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="262.5">
       <c r="A13" s="5">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="14"/>
+        <v>14</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="47.25" x14ac:dyDescent="0.4">
+      <c r="H13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="26.25">
       <c r="A14" s="5">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:11" ht="26.25">
       <c r="A15" s="5">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="14"/>
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H15" s="9"/>
+      <c r="I15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:11" ht="26.25">
       <c r="A16" s="5">
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="17"/>
       <c r="E16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="H16" s="9"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="1:11" ht="262.5">
       <c r="A17" s="5">
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="14"/>
+        <v>23</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H17" s="9"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="1:11" ht="26.25">
       <c r="A18" s="5">
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="14"/>
+        <v>24</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="13"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H18" s="9"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="1:11" ht="26.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="15"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="14"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="1:11" ht="26.25">
       <c r="A20" s="5">
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H20" s="9"/>
+      <c r="I20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="26.25">
       <c r="A21" s="5">
         <v>14</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H21" s="9"/>
+      <c r="I21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="1:11" ht="26.25">
       <c r="A22" s="5">
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H22" s="9"/>
+      <c r="I22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="1:11" ht="26.25">
       <c r="A23" s="5">
         <v>16</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="14"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H23" s="9"/>
+      <c r="I23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="1:11" ht="315">
       <c r="A24" s="5">
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H24" s="9"/>
+      <c r="I24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="26.25">
       <c r="A25" s="5">
         <v>18</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="15"/>
+        <v>34</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H25" s="9"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="1:11" ht="26.25">
       <c r="A26" s="5">
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H26" s="9"/>
+      <c r="I26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+    </row>
+    <row r="27" spans="1:11" ht="26.25">
       <c r="A27" s="5">
         <v>20</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H27" s="9"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28" spans="1:11" ht="26.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29" spans="1:11" ht="26.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" ht="31.5">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
+      <c r="I30" s="23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="31.5">
+      <c r="I31" s="23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="31.5">
+      <c r="I32" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="9:9" ht="31.5">
+      <c r="I33" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="9:9" ht="31.5">
+      <c r="I34" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="9:9" ht="31.5">
+      <c r="I35" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="9:9" ht="31.5">
+      <c r="I36" s="23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="9:9" ht="31.5">
+      <c r="I37" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="9:9" ht="31.5">
+      <c r="I38" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="9:9" ht="31.5">
+      <c r="I39" s="23"/>
+    </row>
+    <row r="40" spans="9:9" ht="31.5">
+      <c r="I40" s="23"/>
+    </row>
+    <row r="41" spans="9:9" ht="31.5">
+      <c r="I41" s="23"/>
+    </row>
+    <row r="42" spans="9:9" ht="31.5">
+      <c r="I42" s="23"/>
+    </row>
+    <row r="43" spans="9:9" ht="31.5">
+      <c r="I43" s="23"/>
+    </row>
+    <row r="44" spans="9:9" ht="31.5">
+      <c r="I44" s="23"/>
+    </row>
+    <row r="45" spans="9:9" ht="31.5">
+      <c r="I45" s="23"/>
+    </row>
+    <row r="46" spans="9:9" ht="31.5">
+      <c r="I46" s="23"/>
+    </row>
+    <row r="47" spans="9:9" ht="31.5">
+      <c r="I47" s="23"/>
+    </row>
+    <row r="48" spans="9:9" ht="31.5">
+      <c r="I48" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491B4E75-DFEB-4274-AF0B-012492219504}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="4" max="4" width="64.5703125" customWidth="1"/>
+    <col min="5" max="5" width="46.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+    </row>
+    <row r="6" spans="1:5" ht="28.5">
+      <c r="A6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57">
+      <c r="A7" s="26"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57">
+      <c r="A8" s="26"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="85.5">
+      <c r="A9" s="26"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="85.5">
+      <c r="A10" s="26"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="114">
+      <c r="A11" s="26"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57">
+      <c r="A12" s="26"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="57">
+      <c r="A13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.5">
+      <c r="A14" s="26"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="85.5">
+      <c r="A15" s="26"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="114">
+      <c r="A16" s="26"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="114">
+      <c r="A17" s="26"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="85.5">
+      <c r="A18" s="26"/>
+      <c r="C18" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="114">
+      <c r="C19" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="142.5">
+      <c r="C20" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="85.5">
+      <c r="C21" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="114">
+      <c r="C22" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="114">
+      <c r="C23" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
